--- a/dcf/AGX.xlsx
+++ b/dcf/AGX.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>288.0976526633838</v>
+        <v>262.5956094540228</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>279.5454115478839</v>
+        <v>255.1354002298817</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>271.3930235823748</v>
+        <v>248.022127118131</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>263.6194455907557</v>
+        <v>241.2375750849428</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>256.2048479234111</v>
+        <v>234.7645782211416</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>249.1305387890354</v>
+        <v>228.5869543728362</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>242.3788936446738</v>
+        <v>222.6894441398043</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>302.4444355214347</v>
+        <v>274.9666057589291</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>293.2286521674528</v>
+        <v>266.9342349107063</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>284.4463239082892</v>
+        <v>259.2777745825449</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>276.0745598007713</v>
+        <v>251.9774164412803</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>268.0917920002559</v>
+        <v>245.0144957605816</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>260.4776931269291</v>
+        <v>238.3714200453273</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>253.2130991626022</v>
+        <v>232.0316024309695</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>316.7912183794857</v>
+        <v>287.3376020638354</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>306.9118927870217</v>
+        <v>278.7330695915308</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>297.4996242342035</v>
+        <v>270.5334220469588</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>288.5296740107869</v>
+        <v>262.7172577976178</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>279.9787360771006</v>
+        <v>255.2644133000216</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>271.8248474648228</v>
+        <v>248.1558857178184</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>264.0473046805307</v>
+        <v>241.3737607221348</v>
       </c>
     </row>
     <row r="8">
@@ -1213,25 +1213,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>331.1380012375366</v>
+        <v>299.7085983687417</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>320.5951334065907</v>
+        <v>290.5319042723554</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>310.5529245601178</v>
+        <v>281.7890695113726</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>300.9847882208026</v>
+        <v>273.4570991539553</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>291.8656801539453</v>
+        <v>265.5143308394616</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>283.1720018027165</v>
+        <v>257.9403513903096</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>274.8815101984592</v>
+        <v>250.7159190133</v>
       </c>
     </row>
     <row r="9">
@@ -1239,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>345.4847840955875</v>
+        <v>312.0795946736479</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>334.2783740261596</v>
+        <v>302.3307389531799</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>323.606224886032</v>
+        <v>293.0447169757866</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>313.4399024308183</v>
+        <v>284.1969405102927</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>303.7526242307901</v>
+        <v>275.7642483789016</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>294.5191561406101</v>
+        <v>267.7248170628007</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>285.7157157163877</v>
+        <v>260.0580773044653</v>
       </c>
     </row>
     <row r="10">
@@ -1265,25 +1265,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>359.8315669536385</v>
+        <v>324.4505909785541</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>347.9616146457286</v>
+        <v>314.1295736340044</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>336.6595252119464</v>
+        <v>304.3003644402004</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>325.8950166408339</v>
+        <v>294.9367818666303</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>315.6395683076349</v>
+        <v>286.0141659183416</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>305.8663104785037</v>
+        <v>277.5092827352918</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>296.5499212343162</v>
+        <v>269.4002355956305</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>374.1783498116894</v>
+        <v>336.8215872834604</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>361.6448552652975</v>
+        <v>325.928408314829</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>349.7128255378607</v>
+        <v>315.5560119046144</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>338.3501308508496</v>
+        <v>305.6766232229677</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>327.5265123844796</v>
+        <v>296.2640834577816</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>317.2134648163974</v>
+        <v>287.2937484077829</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>307.3841267522446</v>
+        <v>278.7423938867958</v>
       </c>
     </row>
     <row r="13">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9968457020240553</v>
+        <v>0.9985178939017954</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>300.9847882208026</v>
+        <v>273.4570991539553</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>413.9368294254063</v>
+        <v>365.5604357609504</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>220.500913471891</v>
+        <v>205.9149777383234</v>
       </c>
     </row>
     <row r="59">
